--- a/scripts/EU_Figures/EU_Figures.xlsx
+++ b/scripts/EU_Figures/EU_Figures.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="E2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="3">
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>0.71</v>
       </c>
       <c r="F4" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.39</v>
+        <v>-0.34</v>
       </c>
       <c r="E5" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="F5" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Labour productivity (per worker)</t>
+          <t>Labour productivity (per hour worked)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.36</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>0.83</v>
+        <v>-0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="7">
@@ -604,17 +604,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025Q2</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0.41</v>
       </c>
       <c r="E7" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="F7" t="n">
-        <v>0.79</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8">
@@ -630,17 +630,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025Q3</t>
+          <t>2025Q2</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="9">
@@ -656,23 +656,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2025Q3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="F9" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Persons employed</t>
+          <t>Labour productivity (per worker)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -682,23 +682,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="F10" t="n">
-        <v>5.16</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Persons employed</t>
+          <t>Labour productivity (per worker)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.18</v>
+        <v>-0.29</v>
       </c>
       <c r="E11" t="n">
-        <v>0.72</v>
+        <v>-0.21</v>
       </c>
       <c r="F11" t="n">
-        <v>5.35</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="12">
@@ -734,17 +734,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025Q3</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.18</v>
       </c>
       <c r="E12" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.54</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="13">
@@ -760,23 +760,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2025Q2</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.18</v>
       </c>
       <c r="E13" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.73</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Real gross value added</t>
+          <t>Persons employed</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -786,23 +786,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2025Q3</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="E14" t="n">
-        <v>1.51</v>
+        <v>0.72</v>
       </c>
       <c r="F14" t="n">
-        <v>6.67</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Real gross value added</t>
+          <t>Persons employed</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -812,23 +812,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025Q2</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>1.43</v>
+        <v>0.72</v>
       </c>
       <c r="F15" t="n">
-        <v>6.82</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Real gross value added</t>
+          <t>Persons employed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025Q3</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.43</v>
+        <v>0.54</v>
       </c>
       <c r="F16" t="n">
-        <v>7.17</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="17">
@@ -864,23 +864,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2025Q1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="F17" t="n">
-        <v>7.37</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Total hours worked</t>
+          <t>Real gross value added</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -890,23 +890,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025Q1</t>
+          <t>2025Q2</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.09</v>
+        <v>0.14</v>
       </c>
       <c r="E18" t="n">
-        <v>0.46</v>
+        <v>1.49</v>
       </c>
       <c r="F18" t="n">
-        <v>4.35</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Total hours worked</t>
+          <t>Real gross value added</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -916,23 +916,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025Q2</t>
+          <t>2025Q3</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.27</v>
+        <v>1.47</v>
       </c>
       <c r="F19" t="n">
-        <v>4.35</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Total hours worked</t>
+          <t>Real gross value added</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -942,43 +942,173 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025Q3</t>
+          <t>2025Q4</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="E20" t="n">
-        <v>0.73</v>
+        <v>1.34</v>
       </c>
       <c r="F20" t="n">
-        <v>4.73</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Real gross value added</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Euro Area</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Total hours worked</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Euro Area</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Euro Area</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total hours worked</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Euro Area</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total hours worked</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Euro Area</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total hours worked</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Euro Area</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>2025Q4</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5.3</v>
+      <c r="D25" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total hours worked</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Euro Area</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.83</v>
       </c>
     </row>
   </sheetData>
@@ -1040,17 +1170,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.39</v>
+        <v>0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>0.44</v>
+        <v>-0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="3">
@@ -1066,17 +1196,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02</v>
+        <v>-0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="F3" t="n">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="4">
@@ -1092,17 +1222,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="F4" t="n">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="5">
@@ -1118,17 +1248,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="E5" t="n">
-        <v>1.34</v>
+        <v>0.29</v>
       </c>
       <c r="F5" t="n">
-        <v>7.37</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="6">
@@ -1144,17 +1274,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>-0.27</v>
       </c>
       <c r="E6" t="n">
-        <v>0.82</v>
+        <v>0.45</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="7">
@@ -1170,17 +1300,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.28</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.74</v>
+        <v>0.15</v>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="8">
@@ -1196,17 +1326,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.83</v>
+        <v>0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="9">
@@ -1222,17 +1352,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
         <v>0.54</v>
       </c>
       <c r="F9" t="n">
-        <v>5.09</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="10">
@@ -1248,17 +1378,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
+        <v>0.64</v>
       </c>
       <c r="F10" t="n">
-        <v>7.95</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="11">
@@ -1274,17 +1404,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.55</v>
+        <v>-0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="F11" t="n">
-        <v>4.66</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="12">
@@ -1300,14 +1430,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="F12" t="n">
         <v>0.35</v>
@@ -1326,17 +1456,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="14">
@@ -1352,14 +1482,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>7.54</v>
@@ -1378,17 +1508,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.18</v>
+        <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.45</v>
+        <v>-0.36</v>
       </c>
       <c r="F15" t="n">
-        <v>6.01</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="16">
@@ -1404,17 +1534,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.78</v>
+        <v>0.58</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="17">
@@ -1430,17 +1560,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="E17" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.72</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1456,17 +1586,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.09</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.19</v>
+        <v>-0.37</v>
       </c>
       <c r="F18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="19">
@@ -1482,17 +1612,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.34</v>
+        <v>0.14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.86</v>
+        <v>0.39</v>
       </c>
       <c r="F19" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="20">
@@ -1508,17 +1638,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.99</v>
+        <v>-0.2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.78</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="21">
@@ -1534,17 +1664,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-5.51</v>
+        <v>-10.49</v>
       </c>
       <c r="E21" t="n">
-        <v>0.32</v>
+        <v>-17.08</v>
       </c>
       <c r="F21" t="n">
-        <v>25.66</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="22">
@@ -1560,17 +1690,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-5.25</v>
+        <v>-11.38</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>-16.87</v>
       </c>
       <c r="F22" t="n">
-        <v>18.85</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="23">
@@ -1586,17 +1716,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.29</v>
+        <v>-0.73</v>
       </c>
       <c r="E23" t="n">
-        <v>1.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>18.76</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="24">
@@ -1612,17 +1742,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2</v>
+        <v>-13.15</v>
       </c>
       <c r="E24" t="n">
-        <v>6.65</v>
+        <v>-12.88</v>
       </c>
       <c r="F24" t="n">
-        <v>49.42</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="25">
@@ -1638,17 +1768,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.52</v>
+        <v>-1.72</v>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>0.31</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="26">
@@ -1664,14 +1794,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.77</v>
+        <v>-0.19</v>
       </c>
       <c r="F26" t="n">
         <v>-2.17</v>
@@ -1690,17 +1820,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.61</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="28">
@@ -1716,17 +1846,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="E28" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="F28" t="n">
-        <v>6.53</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="29">
@@ -1742,17 +1872,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0.25</v>
       </c>
       <c r="E29" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="F29" t="n">
-        <v>7.2</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="30">
@@ -1768,17 +1898,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="E30" t="n">
-        <v>1.62</v>
+        <v>0.98</v>
       </c>
       <c r="F30" t="n">
-        <v>9.49</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1794,17 +1924,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="E31" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="F31" t="n">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="32">
@@ -1820,17 +1950,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.43</v>
+        <v>0.09</v>
       </c>
       <c r="E32" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="33">
@@ -1846,14 +1976,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="F33" t="n">
         <v>7.31</v>
@@ -1872,17 +2002,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="E34" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="F34" t="n">
-        <v>11.05</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="35">
@@ -1898,17 +2028,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.09</v>
+        <v>-0.51</v>
       </c>
       <c r="F35" t="n">
-        <v>5.49</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="36">
@@ -1924,17 +2054,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="E36" t="n">
-        <v>3.27</v>
+        <v>2.84</v>
       </c>
       <c r="F36" t="n">
-        <v>15.61</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="37">
@@ -1950,17 +2080,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="E37" t="n">
-        <v>3.03</v>
+        <v>2.16</v>
       </c>
       <c r="F37" t="n">
-        <v>14.02</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="38">
@@ -1976,17 +2106,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="E38" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="F38" t="n">
-        <v>17.97</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="39">
@@ -2002,14 +2132,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="F39" t="n">
         <v>2.51</v>
@@ -2028,17 +2158,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-0.28</v>
+        <v>0.96</v>
       </c>
       <c r="E40" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="F40" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="41">
@@ -2054,17 +2184,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.04</v>
+        <v>0.25</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.3</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="42">
@@ -2080,17 +2210,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.74</v>
+        <v>0.33</v>
       </c>
       <c r="E42" t="n">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="F42" t="n">
-        <v>10.94</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="43">
@@ -2106,17 +2236,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="E43" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="F43" t="n">
-        <v>11.97</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="44">
@@ -2132,17 +2262,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.02</v>
+        <v>-0.34</v>
       </c>
       <c r="E44" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="F44" t="n">
-        <v>8.779999999999999</v>
+        <v>8.42</v>
       </c>
     </row>
   </sheetData>
